--- a/templates/test_files/Data Dictionary_BdCH_AreaMgmt_v0.9.4.xlsx
+++ b/templates/test_files/Data Dictionary_BdCH_AreaMgmt_v0.9.4.xlsx
@@ -19,19 +19,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="Base_Type">Rules!$L$2:$L$47</definedName>
-    <definedName name="Beschreibung">Rules!$M$2:$M$47</definedName>
-    <definedName name="Category">Rules!$K$2:$K$47</definedName>
-    <definedName name="DataType">Rules!$I$2:$I$47</definedName>
-    <definedName name="FAIR_Prinzipien">Rules!$P$2:$P$47</definedName>
-    <definedName name="IFC_Data_Type">Rules!$J$2:$J$47</definedName>
-    <definedName name="ISG___Informationssicherheitsgesetz">Rules!$O$2:$O$47</definedName>
+    <definedName name="DataType">'Rules'!$I$2:$I$47</definedName>
+    <definedName name="FAIR_Prinzipien">'Rules'!$M$2:$M$47</definedName>
+    <definedName name="IFC_Data_Type">'Rules'!$J$2:$J$47</definedName>
+    <definedName name="ISG___Informationssicherheitsgesetz">'Rules'!$L$2:$L$47</definedName>
     <definedName name="Klassifikation">Rules!$B$2:$B$47</definedName>
-    <definedName name="LifecycleStatus">Rules!$Q$2:$Q$47</definedName>
-    <definedName name="Objekt_Einordnung">Rules!$A$2:$A$47</definedName>
-    <definedName name="Property_Classification">Rules!$E$2:$E$47</definedName>
-    <definedName name="Status">Rules!$N$2:$N$47</definedName>
+    <definedName name="LifecycleStatus">'Rules'!$N$2:$N$47</definedName>
+    <definedName name="Objekt_Einordnung">'Rules'!$A$2:$A$47</definedName>
+    <definedName name="Property_Classification">'Rules'!$E$2:$E$47</definedName>
+    <definedName name="Status">'Rules'!$K$2:$K$47</definedName>
     <definedName name="Markmals_Klassifikation">'Rules'!$F$2:$F$47</definedName>
+    <definedName name="Class-Assignment">'Rules'!$A$2:$A$47</definedName>
+    <definedName name="Klassen_Zuordnung">'Rules'!$B$2:$B$47</definedName>
+    <definedName name="Affectation_de_classe">'Rules'!$C$2:$C$47</definedName>
+    <definedName name="Assegnazione_della_classe">'Rules'!$D$2:$D$47</definedName>
+    <definedName name="Merkmals_Zuordnung">'Rules'!$F$2:$F$47</definedName>
+    <definedName name="Attribution_de_propriete">'Rules'!$G$2:$G$47</definedName>
+    <definedName name="Assegnazione_della_proprieta">'Rules'!$H$2:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Classes'!$A$6:$AE$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Properties'!$A$6:$Z$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Values'!$A$6:$S$6</definedName>
@@ -3995,7 +3999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="253" min="1" max="1"/>
@@ -4070,35 +4074,20 @@
       </c>
       <c r="K1" s="244" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="L1" s="244" t="inlineStr">
         <is>
-          <t>Base Type</t>
+          <t>ISG - Informationssicherheitsgesetz</t>
         </is>
       </c>
       <c r="M1" s="244" t="inlineStr">
         <is>
-          <t>Beschreibung</t>
+          <t>FAIR Prinzipien</t>
         </is>
       </c>
       <c r="N1" s="244" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="O1" s="244" t="inlineStr">
-        <is>
-          <t>ISG - Informationssicherheitsgesetz</t>
-        </is>
-      </c>
-      <c r="P1" s="244" t="inlineStr">
-        <is>
-          <t>FAIR Prinzipien</t>
-        </is>
-      </c>
-      <c r="Q1" s="244" t="inlineStr">
         <is>
           <t>LifecycleStatus</t>
         </is>
@@ -4157,31 +4146,20 @@
       </c>
       <c r="K2" s="39" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Preview</t>
         </is>
       </c>
       <c r="L2" s="39" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M2" s="39" t="n"/>
+          <t>nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="M2" s="39" t="inlineStr">
+        <is>
+          <t>Zugänglich kostenpflichtig</t>
+        </is>
+      </c>
       <c r="N2" s="39" t="inlineStr">
-        <is>
-          <t>Preview</t>
-        </is>
-      </c>
-      <c r="O2" s="39" t="inlineStr">
-        <is>
-          <t>nicht klassifiziert</t>
-        </is>
-      </c>
-      <c r="P2" s="39" t="inlineStr">
-        <is>
-          <t>Zugänglich kostenpflichtig</t>
-        </is>
-      </c>
-      <c r="Q2" s="39" t="inlineStr">
         <is>
           <t>Preview</t>
         </is>
@@ -4240,35 +4218,20 @@
       </c>
       <c r="K3" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="L3" s="39" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="M3" s="39" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t>Zugänglich unentgeltlich</t>
         </is>
       </c>
       <c r="N3" s="39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="O3" s="39" t="inlineStr">
-        <is>
-          <t>intern</t>
-        </is>
-      </c>
-      <c r="P3" s="39" t="inlineStr">
-        <is>
-          <t>Zugänglich unentgeltlich</t>
-        </is>
-      </c>
-      <c r="Q3" s="39" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -4327,35 +4290,20 @@
       </c>
       <c r="K4" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="L4" s="39" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>sensitiv</t>
         </is>
       </c>
       <c r="M4" s="39" t="inlineStr">
         <is>
-          <t>Datum und Zeit</t>
+          <t>Nicht zugänglich - kostenpflichtig</t>
         </is>
       </c>
       <c r="N4" s="39" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="O4" s="39" t="inlineStr">
-        <is>
-          <t>sensitiv</t>
-        </is>
-      </c>
-      <c r="P4" s="39" t="inlineStr">
-        <is>
-          <t>Nicht zugänglich - kostenpflichtig</t>
-        </is>
-      </c>
-      <c r="Q4" s="39" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
@@ -4414,35 +4362,20 @@
       </c>
       <c r="K5" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
+          <t>Deprecated</t>
         </is>
       </c>
       <c r="L5" s="39" t="inlineStr">
         <is>
-          <t>STRING</t>
+          <t>geheim</t>
         </is>
       </c>
       <c r="M5" s="39" t="inlineStr">
         <is>
-          <t>Zeitdauer</t>
+          <t>Nicht zugänglich - unentgeltlich</t>
         </is>
       </c>
       <c r="N5" s="39" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="O5" s="39" t="inlineStr">
-        <is>
-          <t>geheim</t>
-        </is>
-      </c>
-      <c r="P5" s="39" t="inlineStr">
-        <is>
-          <t>Nicht zugänglich - unentgeltlich</t>
-        </is>
-      </c>
-      <c r="Q5" s="39" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
@@ -4501,27 +4434,12 @@
       </c>
       <c r="K6" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L6" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M6" s="39" t="inlineStr">
-        <is>
-          <t>Globale eindeutige ID</t>
-        </is>
-      </c>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="L6" s="39" t="n"/>
+      <c r="M6" s="39" t="n"/>
       <c r="N6" s="39" t="inlineStr">
-        <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="O6" s="39" t="n"/>
-      <c r="P6" s="39" t="n"/>
-      <c r="Q6" s="39" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
@@ -4580,27 +4498,12 @@
       </c>
       <c r="K7" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L7" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M7" s="39" t="inlineStr">
-        <is>
-          <t>Eindeutiger Identifikator</t>
-        </is>
-      </c>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="L7" s="39" t="n"/>
+      <c r="M7" s="39" t="n"/>
       <c r="N7" s="39" t="inlineStr">
-        <is>
-          <t>Candidate</t>
-        </is>
-      </c>
-      <c r="O7" s="39" t="n"/>
-      <c r="P7" s="39" t="n"/>
-      <c r="Q7" s="39" t="inlineStr">
         <is>
           <t>Candidate</t>
         </is>
@@ -4659,27 +4562,12 @@
       </c>
       <c r="K8" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L8" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M8" s="39" t="inlineStr">
-        <is>
-          <t>Ganzzahl</t>
-        </is>
-      </c>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="L8" s="39" t="n"/>
+      <c r="M8" s="39" t="n"/>
       <c r="N8" s="39" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="O8" s="39" t="n"/>
-      <c r="P8" s="39" t="n"/>
-      <c r="Q8" s="39" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -4734,27 +4622,12 @@
       </c>
       <c r="K9" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L9" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M9" s="39" t="inlineStr">
-        <is>
-          <t>Lokale Uhrzeit</t>
-        </is>
-      </c>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="L9" s="39" t="n"/>
+      <c r="M9" s="39" t="n"/>
       <c r="N9" s="39" t="inlineStr">
-        <is>
-          <t>Superseded</t>
-        </is>
-      </c>
-      <c r="O9" s="39" t="n"/>
-      <c r="P9" s="39" t="n"/>
-      <c r="Q9" s="39" t="inlineStr">
         <is>
           <t>Superseded</t>
         </is>
@@ -4793,27 +4666,12 @@
       </c>
       <c r="K10" s="39" t="inlineStr">
         <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L10" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M10" s="39" t="inlineStr">
-        <is>
-          <t>Logischer Wert</t>
-        </is>
-      </c>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L10" s="39" t="n"/>
+      <c r="M10" s="39" t="n"/>
       <c r="N10" s="39" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-      <c r="O10" s="39" t="n"/>
-      <c r="P10" s="39" t="n"/>
-      <c r="Q10" s="39" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
@@ -4850,25 +4708,10 @@
           <t>IfcLengthMeasure</t>
         </is>
       </c>
-      <c r="K11" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L11" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M11" s="39" t="inlineStr">
-        <is>
-          <t>Mass für Länge</t>
-        </is>
-      </c>
+      <c r="K11" s="39" t="n"/>
+      <c r="L11" s="39" t="n"/>
+      <c r="M11" s="39" t="n"/>
       <c r="N11" s="39" t="n"/>
-      <c r="O11" s="39" t="n"/>
-      <c r="P11" s="39" t="n"/>
-      <c r="Q11" s="39" t="n"/>
     </row>
     <row r="12" customFormat="1" s="72">
       <c r="A12" s="77" t="n"/>
@@ -4901,25 +4744,10 @@
           <t>IfcLocalTime</t>
         </is>
       </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L12" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M12" s="39" t="inlineStr">
-        <is>
-          <t>Positiver Ganzzahlwert</t>
-        </is>
-      </c>
+      <c r="K12" s="39" t="n"/>
+      <c r="L12" s="39" t="n"/>
+      <c r="M12" s="39" t="n"/>
       <c r="N12" s="39" t="n"/>
-      <c r="O12" s="39" t="n"/>
-      <c r="P12" s="39" t="n"/>
-      <c r="Q12" s="39" t="n"/>
     </row>
     <row r="13" customFormat="1" s="72">
       <c r="A13" s="77" t="n"/>
@@ -4952,25 +4780,10 @@
           <t>IfcLogical</t>
         </is>
       </c>
-      <c r="K13" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L13" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M13" s="39" t="inlineStr">
-        <is>
-          <t>Positiver Längenwert</t>
-        </is>
-      </c>
+      <c r="K13" s="39" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="39" t="n"/>
       <c r="N13" s="39" t="n"/>
-      <c r="O13" s="39" t="n"/>
-      <c r="P13" s="39" t="n"/>
-      <c r="Q13" s="39" t="n"/>
     </row>
     <row r="14" customFormat="1" s="72">
       <c r="A14" s="77" t="n"/>
@@ -5003,25 +4816,10 @@
           <t>IfcNormalisedRatioMeasure</t>
         </is>
       </c>
-      <c r="K14" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L14" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M14" s="39" t="inlineStr">
-        <is>
-          <t>Positiver Verhältniswert</t>
-        </is>
-      </c>
+      <c r="K14" s="39" t="n"/>
+      <c r="L14" s="39" t="n"/>
+      <c r="M14" s="39" t="n"/>
       <c r="N14" s="39" t="n"/>
-      <c r="O14" s="39" t="n"/>
-      <c r="P14" s="39" t="n"/>
-      <c r="Q14" s="39" t="n"/>
     </row>
     <row r="15" customFormat="1" s="72">
       <c r="A15" s="77" t="n"/>
@@ -5054,25 +4852,10 @@
           <t>IfcPositiveInteger</t>
         </is>
       </c>
-      <c r="K15" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L15" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M15" s="39" t="inlineStr">
-        <is>
-          <t>Positives Zeitmass</t>
-        </is>
-      </c>
+      <c r="K15" s="39" t="n"/>
+      <c r="L15" s="39" t="n"/>
+      <c r="M15" s="39" t="n"/>
       <c r="N15" s="39" t="n"/>
-      <c r="O15" s="39" t="n"/>
-      <c r="P15" s="39" t="n"/>
-      <c r="Q15" s="39" t="n"/>
     </row>
     <row r="16" customFormat="1" s="72">
       <c r="A16" s="77" t="n"/>
@@ -5105,25 +4888,10 @@
           <t>IfcPositiveLengthMeasure</t>
         </is>
       </c>
-      <c r="K16" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L16" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M16" s="39" t="inlineStr">
-        <is>
-          <t>Reelle Zahl</t>
-        </is>
-      </c>
+      <c r="K16" s="39" t="n"/>
+      <c r="L16" s="39" t="n"/>
+      <c r="M16" s="39" t="n"/>
       <c r="N16" s="39" t="n"/>
-      <c r="O16" s="39" t="n"/>
-      <c r="P16" s="39" t="n"/>
-      <c r="Q16" s="39" t="n"/>
     </row>
     <row r="17" customFormat="1" s="72">
       <c r="A17" s="77" t="n"/>
@@ -5156,25 +4924,10 @@
           <t>IfcPositiveRatioMeasure</t>
         </is>
       </c>
-      <c r="K17" s="39" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L17" s="39" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M17" s="39" t="inlineStr">
-        <is>
-          <t>Verhältniswert</t>
-        </is>
-      </c>
+      <c r="K17" s="39" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="39" t="n"/>
       <c r="N17" s="39" t="n"/>
-      <c r="O17" s="39" t="n"/>
-      <c r="P17" s="39" t="n"/>
-      <c r="Q17" s="39" t="n"/>
     </row>
     <row r="18" customFormat="1" s="72">
       <c r="A18" s="77" t="n"/>
@@ -5191,25 +4944,10 @@
           <t>IfcPositiveTimeMeasure</t>
         </is>
       </c>
-      <c r="K18" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L18" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M18" s="78" t="inlineStr">
-        <is>
-          <t>Thermischer Transmissionskoeffizient</t>
-        </is>
-      </c>
+      <c r="K18" s="78" t="n"/>
+      <c r="L18" s="78" t="n"/>
+      <c r="M18" s="78" t="n"/>
       <c r="N18" s="78" t="n"/>
-      <c r="O18" s="78" t="n"/>
-      <c r="P18" s="78" t="n"/>
-      <c r="Q18" s="78" t="n"/>
     </row>
     <row r="19" customFormat="1" s="72">
       <c r="A19" s="77" t="n"/>
@@ -5226,25 +4964,10 @@
           <t>IfcRatioMeasure</t>
         </is>
       </c>
-      <c r="K19" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L19" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M19" s="78" t="inlineStr">
-        <is>
-          <t>Textwert</t>
-        </is>
-      </c>
+      <c r="K19" s="78" t="n"/>
+      <c r="L19" s="78" t="n"/>
+      <c r="M19" s="78" t="n"/>
       <c r="N19" s="78" t="n"/>
-      <c r="O19" s="78" t="n"/>
-      <c r="P19" s="78" t="n"/>
-      <c r="Q19" s="78" t="n"/>
     </row>
     <row r="20" customFormat="1" s="72">
       <c r="A20" s="77" t="n"/>
@@ -5261,25 +4984,10 @@
           <t>IfcReal</t>
         </is>
       </c>
-      <c r="K20" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L20" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M20" s="78" t="inlineStr">
-        <is>
-          <t>Zeitangabe</t>
-        </is>
-      </c>
+      <c r="K20" s="78" t="n"/>
+      <c r="L20" s="78" t="n"/>
+      <c r="M20" s="78" t="n"/>
       <c r="N20" s="78" t="n"/>
-      <c r="O20" s="78" t="n"/>
-      <c r="P20" s="78" t="n"/>
-      <c r="Q20" s="78" t="n"/>
     </row>
     <row r="21" customFormat="1" s="72">
       <c r="A21" s="77" t="n"/>
@@ -5296,25 +5004,10 @@
           <t>IfcText</t>
         </is>
       </c>
-      <c r="K21" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L21" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M21" s="78" t="inlineStr">
-        <is>
-          <t>URI-Referenz</t>
-        </is>
-      </c>
+      <c r="K21" s="78" t="n"/>
+      <c r="L21" s="78" t="n"/>
+      <c r="M21" s="78" t="n"/>
       <c r="N21" s="78" t="n"/>
-      <c r="O21" s="78" t="n"/>
-      <c r="P21" s="78" t="n"/>
-      <c r="Q21" s="78" t="n"/>
     </row>
     <row r="22" customFormat="1" s="72">
       <c r="A22" s="77" t="n"/>
@@ -5331,25 +5024,10 @@
           <t>IfcThermalTransmittanceMeasure</t>
         </is>
       </c>
-      <c r="K22" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L22" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M22" s="78" t="inlineStr">
-        <is>
-          <t>Wahr/Falsch-Wert</t>
-        </is>
-      </c>
+      <c r="K22" s="78" t="n"/>
+      <c r="L22" s="78" t="n"/>
+      <c r="M22" s="78" t="n"/>
       <c r="N22" s="78" t="n"/>
-      <c r="O22" s="78" t="n"/>
-      <c r="P22" s="78" t="n"/>
-      <c r="Q22" s="78" t="n"/>
     </row>
     <row r="23" customFormat="1" s="72">
       <c r="A23" s="77" t="n"/>
@@ -5366,25 +5044,10 @@
           <t>IfcTime</t>
         </is>
       </c>
-      <c r="K23" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L23" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M23" s="78" t="inlineStr">
-        <is>
-          <t>Zeichenwert</t>
-        </is>
-      </c>
+      <c r="K23" s="78" t="n"/>
+      <c r="L23" s="78" t="n"/>
+      <c r="M23" s="78" t="n"/>
       <c r="N23" s="78" t="n"/>
-      <c r="O23" s="78" t="n"/>
-      <c r="P23" s="78" t="n"/>
-      <c r="Q23" s="78" t="n"/>
     </row>
     <row r="24" customFormat="1" s="72">
       <c r="A24" s="77" t="n"/>
@@ -5401,25 +5064,10 @@
           <t>IfcURIReference</t>
         </is>
       </c>
-      <c r="K24" s="78" t="inlineStr">
-        <is>
-          <t>Simple Defined Type</t>
-        </is>
-      </c>
-      <c r="L24" s="78" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="M24" s="78" t="inlineStr">
-        <is>
-          <t>Beschriftung</t>
-        </is>
-      </c>
+      <c r="K24" s="78" t="n"/>
+      <c r="L24" s="78" t="n"/>
+      <c r="M24" s="78" t="n"/>
       <c r="N24" s="78" t="n"/>
-      <c r="O24" s="78" t="n"/>
-      <c r="P24" s="78" t="n"/>
-      <c r="Q24" s="78" t="n"/>
     </row>
     <row r="25" customFormat="1" s="72">
       <c r="A25" s="77" t="n"/>
@@ -5436,9 +5084,6 @@
       <c r="L25" s="78" t="n"/>
       <c r="M25" s="78" t="n"/>
       <c r="N25" s="78" t="n"/>
-      <c r="O25" s="78" t="n"/>
-      <c r="P25" s="78" t="n"/>
-      <c r="Q25" s="78" t="n"/>
     </row>
     <row r="26" customFormat="1" s="72">
       <c r="A26" s="77" t="n"/>
@@ -5455,9 +5100,6 @@
       <c r="L26" s="78" t="n"/>
       <c r="M26" s="78" t="n"/>
       <c r="N26" s="78" t="n"/>
-      <c r="O26" s="78" t="n"/>
-      <c r="P26" s="78" t="n"/>
-      <c r="Q26" s="78" t="n"/>
     </row>
     <row r="27" customFormat="1" s="72">
       <c r="A27" s="77" t="n"/>
@@ -5474,9 +5116,6 @@
       <c r="L27" s="78" t="n"/>
       <c r="M27" s="78" t="n"/>
       <c r="N27" s="78" t="n"/>
-      <c r="O27" s="78" t="n"/>
-      <c r="P27" s="78" t="n"/>
-      <c r="Q27" s="78" t="n"/>
     </row>
     <row r="28" customFormat="1" s="72">
       <c r="A28" s="77" t="n"/>
@@ -5493,9 +5132,6 @@
       <c r="L28" s="78" t="n"/>
       <c r="M28" s="78" t="n"/>
       <c r="N28" s="78" t="n"/>
-      <c r="O28" s="78" t="n"/>
-      <c r="P28" s="78" t="n"/>
-      <c r="Q28" s="78" t="n"/>
     </row>
     <row r="29" customFormat="1" s="72">
       <c r="A29" s="77" t="n"/>
@@ -5512,9 +5148,6 @@
       <c r="L29" s="78" t="n"/>
       <c r="M29" s="78" t="n"/>
       <c r="N29" s="78" t="n"/>
-      <c r="O29" s="78" t="n"/>
-      <c r="P29" s="78" t="n"/>
-      <c r="Q29" s="78" t="n"/>
     </row>
     <row r="30" customFormat="1" s="72">
       <c r="A30" s="77" t="n"/>
@@ -5531,9 +5164,6 @@
       <c r="L30" s="167" t="n"/>
       <c r="M30" s="167" t="n"/>
       <c r="N30" s="167" t="n"/>
-      <c r="O30" s="167" t="n"/>
-      <c r="P30" s="167" t="n"/>
-      <c r="Q30" s="167" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="77" t="n"/>
@@ -5550,9 +5180,6 @@
       <c r="L31" s="167" t="n"/>
       <c r="M31" s="167" t="n"/>
       <c r="N31" s="167" t="n"/>
-      <c r="O31" s="167" t="n"/>
-      <c r="P31" s="167" t="n"/>
-      <c r="Q31" s="167" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="77" t="n"/>
@@ -5569,9 +5196,6 @@
       <c r="L32" s="167" t="n"/>
       <c r="M32" s="167" t="n"/>
       <c r="N32" s="167" t="n"/>
-      <c r="O32" s="167" t="n"/>
-      <c r="P32" s="167" t="n"/>
-      <c r="Q32" s="167" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="77" t="n"/>
@@ -5588,9 +5212,6 @@
       <c r="L33" s="167" t="n"/>
       <c r="M33" s="167" t="n"/>
       <c r="N33" s="167" t="n"/>
-      <c r="O33" s="167" t="n"/>
-      <c r="P33" s="167" t="n"/>
-      <c r="Q33" s="167" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="77" t="n"/>
@@ -5607,9 +5228,6 @@
       <c r="L34" s="167" t="n"/>
       <c r="M34" s="167" t="n"/>
       <c r="N34" s="167" t="n"/>
-      <c r="O34" s="167" t="n"/>
-      <c r="P34" s="167" t="n"/>
-      <c r="Q34" s="167" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="77" t="n"/>
@@ -5626,9 +5244,6 @@
       <c r="L35" s="167" t="n"/>
       <c r="M35" s="167" t="n"/>
       <c r="N35" s="167" t="n"/>
-      <c r="O35" s="167" t="n"/>
-      <c r="P35" s="167" t="n"/>
-      <c r="Q35" s="167" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="77" t="n"/>
@@ -5645,9 +5260,6 @@
       <c r="L36" s="167" t="n"/>
       <c r="M36" s="167" t="n"/>
       <c r="N36" s="167" t="n"/>
-      <c r="O36" s="167" t="n"/>
-      <c r="P36" s="167" t="n"/>
-      <c r="Q36" s="167" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="77" t="n"/>
@@ -5664,9 +5276,6 @@
       <c r="L37" s="167" t="n"/>
       <c r="M37" s="167" t="n"/>
       <c r="N37" s="167" t="n"/>
-      <c r="O37" s="167" t="n"/>
-      <c r="P37" s="167" t="n"/>
-      <c r="Q37" s="167" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="77" t="n"/>
@@ -5683,9 +5292,6 @@
       <c r="L38" s="167" t="n"/>
       <c r="M38" s="167" t="n"/>
       <c r="N38" s="167" t="n"/>
-      <c r="O38" s="167" t="n"/>
-      <c r="P38" s="167" t="n"/>
-      <c r="Q38" s="167" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="77" t="n"/>
@@ -5702,9 +5308,6 @@
       <c r="L39" s="167" t="n"/>
       <c r="M39" s="167" t="n"/>
       <c r="N39" s="167" t="n"/>
-      <c r="O39" s="167" t="n"/>
-      <c r="P39" s="167" t="n"/>
-      <c r="Q39" s="167" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="77" t="n"/>
@@ -5721,9 +5324,6 @@
       <c r="L40" s="167" t="n"/>
       <c r="M40" s="167" t="n"/>
       <c r="N40" s="167" t="n"/>
-      <c r="O40" s="167" t="n"/>
-      <c r="P40" s="167" t="n"/>
-      <c r="Q40" s="167" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="77" t="n"/>
@@ -5740,9 +5340,6 @@
       <c r="L41" s="167" t="n"/>
       <c r="M41" s="167" t="n"/>
       <c r="N41" s="167" t="n"/>
-      <c r="O41" s="167" t="n"/>
-      <c r="P41" s="167" t="n"/>
-      <c r="Q41" s="167" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="77" t="n"/>
@@ -5759,9 +5356,6 @@
       <c r="L42" s="167" t="n"/>
       <c r="M42" s="167" t="n"/>
       <c r="N42" s="167" t="n"/>
-      <c r="O42" s="167" t="n"/>
-      <c r="P42" s="167" t="n"/>
-      <c r="Q42" s="167" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="77" t="n"/>
@@ -5778,9 +5372,6 @@
       <c r="L43" s="167" t="n"/>
       <c r="M43" s="167" t="n"/>
       <c r="N43" s="167" t="n"/>
-      <c r="O43" s="167" t="n"/>
-      <c r="P43" s="167" t="n"/>
-      <c r="Q43" s="167" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="77" t="n"/>
@@ -5797,9 +5388,6 @@
       <c r="L44" s="167" t="n"/>
       <c r="M44" s="167" t="n"/>
       <c r="N44" s="167" t="n"/>
-      <c r="O44" s="167" t="n"/>
-      <c r="P44" s="167" t="n"/>
-      <c r="Q44" s="167" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="77" t="n"/>
@@ -5816,9 +5404,6 @@
       <c r="L45" s="167" t="n"/>
       <c r="M45" s="167" t="n"/>
       <c r="N45" s="167" t="n"/>
-      <c r="O45" s="167" t="n"/>
-      <c r="P45" s="167" t="n"/>
-      <c r="Q45" s="167" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="77" t="n"/>
@@ -5835,9 +5420,6 @@
       <c r="L46" s="167" t="n"/>
       <c r="M46" s="167" t="n"/>
       <c r="N46" s="167" t="n"/>
-      <c r="O46" s="167" t="n"/>
-      <c r="P46" s="167" t="n"/>
-      <c r="Q46" s="167" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="77" t="n"/>
@@ -5854,9 +5436,6 @@
       <c r="L47" s="167" t="n"/>
       <c r="M47" s="167" t="n"/>
       <c r="N47" s="167" t="n"/>
-      <c r="O47" s="167" t="n"/>
-      <c r="P47" s="167" t="n"/>
-      <c r="Q47" s="167" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7874015748031497" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
@@ -12681,18 +12260,24 @@
     </row>
   </sheetData>
   <autoFilter ref="A6:AE6"/>
-  <dataValidations xWindow="1091" yWindow="456" count="4">
+  <dataValidations xWindow="1091" yWindow="456" count="6">
     <dataValidation sqref="AB7:AB1996" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="date" operator="greaterThanOrEqual">
       <formula1>DATE(2000,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Objekt_Einordnung</formula1>
+    <dataValidation sqref="AD7:AD1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Status</formula1>
     </dataValidation>
     <dataValidation sqref="K7:K1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Objekt_Einordnung</formula1>
     </dataValidation>
-    <dataValidation sqref="AD7:AD1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Status</formula1>
+    <dataValidation sqref="L7:L1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Klassen_Zuordnung</formula1>
+    </dataValidation>
+    <dataValidation sqref="M7:M1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Affectation_de_classe</formula1>
+    </dataValidation>
+    <dataValidation sqref="N7:N1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Assegnazione_della_classe</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -20511,7 +20096,7 @@
     <row r="354" ht="13.5" customHeight="1" s="253"/>
   </sheetData>
   <autoFilter ref="A6:Z6"/>
-  <dataValidations count="6">
+  <dataValidations count="9">
     <dataValidation sqref="L2:L59 L247:L1997" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Beschreibung</formula1>
     </dataValidation>
@@ -20530,6 +20115,15 @@
     </dataValidation>
     <dataValidation sqref="G7:G1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Property_Classification</formula1>
+    </dataValidation>
+    <dataValidation sqref="H7:H1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Merkmals_Zuordnung</formula1>
+    </dataValidation>
+    <dataValidation sqref="I7:I1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Attribution_de_propriete</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Assegnazione_della_proprieta</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7874015748031497" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>

--- a/templates/test_files/Data Dictionary_BdCH_AreaMgmt_v0.9.4.xlsx
+++ b/templates/test_files/Data Dictionary_BdCH_AreaMgmt_v0.9.4.xlsx
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B4" s="245" t="inlineStr">
         <is>
-          <t>DataDic</t>
+          <t>BdCH</t>
         </is>
       </c>
       <c r="C4" s="248" t="inlineStr">
         <is>
-          <t>REQUIRED</t>
+          <t>user defined name (small or capital letters), max 7 chars</t>
         </is>
       </c>
       <c r="D4" s="245" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://example.com/DataDic/data_dictionary_area_management</t>
+          <t>https://example.com/BdCH/data_dictionary_area_management</t>
         </is>
       </c>
       <c r="C11" s="248" t="inlineStr">
@@ -26036,7 +26036,7 @@
       <c r="E7" s="198" t="n"/>
       <c r="F7" s="198" t="inlineStr">
         <is>
-          <t>DataDic_AreaMgmt</t>
+          <t>BdCH_AreaMgmt</t>
         </is>
       </c>
       <c r="G7" s="198" t="inlineStr">
